--- a/Gurobi_QAP_Benchmark.xlsx
+++ b/Gurobi_QAP_Benchmark.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,20 +436,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>Gurobi_Obj</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Gurobi_Obj</t>
+          <t>Known_Opt</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Known_Opt</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Solve_Time(s)</t>
         </is>
@@ -458,20 +453,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nug12</t>
+          <t>bl100</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C2" t="n">
-        <v>578</v>
-      </c>
+        <v>9558</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>578</v>
-      </c>
-      <c r="E2" t="n">
-        <v>115.3270318508148</v>
+        <v>1200.103992462158</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bl121</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>25884</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>1200.334055185318</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bl144</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>30606</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>1240.883138656616</v>
       </c>
     </row>
   </sheetData>
